--- a/public/reports/n400/Dissertatsiya_Tahlil_N400.xlsx
+++ b/public/reports/n400/Dissertatsiya_Tahlil_N400.xlsx
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,6 +747,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Izoh</t>
         </is>
       </c>
@@ -768,6 +773,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>29.4–38.6</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>Asosiy yuqori foizdagi kasallik</t>
         </is>
       </c>
@@ -789,6 +799,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>22.6–31.4</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>Asosiy yuqori foizdagi kasallik</t>
         </is>
       </c>
@@ -810,6 +825,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>13.3–20.7</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Asosiy yuqori foizdagi kasallik</t>
         </is>
       </c>
@@ -831,6 +851,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>7.9–14.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>Qo'shimcha kasallik guruhi</t>
         </is>
       </c>
@@ -852,6 +877,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>4.5–9.5</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Qo'shimcha kasallik guruhi</t>
         </is>
       </c>
@@ -872,6 +902,11 @@
         <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>2.1–5.9</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Qo'shimcha kasallik guruhi</t>
         </is>
@@ -888,7 +923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +949,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>95% CI</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>100 ishchiga</t>
         </is>
       </c>
@@ -935,7 +975,12 @@
       <c r="D2" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -956,7 +1001,12 @@
       <c r="D3" t="n">
         <v>0.5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -977,7 +1027,12 @@
       <c r="D4" t="n">
         <v>0.5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -998,7 +1053,12 @@
       <c r="D5" t="n">
         <v>0.8</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.0–1.6</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -1019,7 +1079,12 @@
       <c r="D6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1040,7 +1105,12 @@
       <c r="D7" t="n">
         <v>10.2</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7.3–13.2</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>10.2</v>
       </c>
     </row>
@@ -1061,7 +1131,12 @@
       <c r="D8" t="n">
         <v>0.5</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1082,7 +1157,12 @@
       <c r="D9" t="n">
         <v>0.5</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1103,7 +1183,12 @@
       <c r="D10" t="n">
         <v>16</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12.4–19.6</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1124,7 +1209,12 @@
       <c r="D11" t="n">
         <v>31.8</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>27.2–36.3</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>31.8</v>
       </c>
     </row>
@@ -1145,7 +1235,12 @@
       <c r="D12" t="n">
         <v>3.8</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.9–5.6</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
         <v>3.8</v>
       </c>
     </row>
@@ -1166,7 +1261,12 @@
       <c r="D13" t="n">
         <v>0.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1187,7 +1287,12 @@
       <c r="D14" t="n">
         <v>25.2</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>21.0–29.5</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>25.2</v>
       </c>
     </row>
@@ -1208,7 +1313,12 @@
       <c r="D15" t="n">
         <v>6.5</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4.1–8.9</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -1229,7 +1339,12 @@
       <c r="D16" t="n">
         <v>0.5</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1250,7 +1365,12 @@
       <c r="D17" t="n">
         <v>0.5</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1271,7 +1391,12 @@
       <c r="D18" t="n">
         <v>0.2</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.0–0.7</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1292,7 +1417,12 @@
       <c r="D19" t="n">
         <v>0.5</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1313,7 +1443,12 @@
       <c r="D20" t="n">
         <v>0.5</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.0–1.2</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
         <v>0.5</v>
       </c>
     </row>
